--- a/rentacar/exword_results/statement.xlsx
+++ b/rentacar/exword_results/statement.xlsx
@@ -164,9 +164,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -178,17 +175,20 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -561,7 +561,7 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -602,11 +602,11 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>11.04.2025</t>
+          <t>20.04.2025</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0</v>
+        <v>400.1</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
       </c>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="5" t="n">
-        <v>21.7</v>
+        <v>378.4</v>
       </c>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="1" t="inlineStr">
@@ -637,20 +637,20 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>07.04.2025</t>
+          <t>19.04.2025</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>21.7</v>
+        <v>421.8</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Toll: 8.8</t>
+          <t>Charging of rental: 21.7</t>
         </is>
       </c>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="5" t="n">
-        <v>30.5</v>
+        <v>400.1</v>
       </c>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
@@ -664,24 +664,20 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>09.12.2024</t>
+          <t>18.04.2025</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>30.5</v>
+        <v>443.5</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Charging of rental: 650</t>
+          <t>Charging of rental: 21.7</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Rent payment: 650</t>
-        </is>
-      </c>
+      <c r="D4" s="3" t="n"/>
       <c r="E4" s="5" t="n">
-        <v>30.5</v>
+        <v>421.8</v>
       </c>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
@@ -695,20 +691,20 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>18.12.2024</t>
+          <t>17.04.2025</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>30.5</v>
+        <v>465.2</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>100$ Денису должен за выезд : 100</t>
+          <t>Charging of rental: 21.7</t>
         </is>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="5" t="n">
-        <v>130.5</v>
+        <v>443.5</v>
       </c>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
@@ -720,22 +716,22 @@
       <c r="M5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>09.02.2025</t>
+          <t>16.04.2025</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
-        <v>130.5</v>
+      <c r="B6" s="3" t="n">
+        <v>486.9</v>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Charging of rental: 650</t>
+          <t>Charging of rental: 21.7</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="10" t="n">
-        <v>796.5</v>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="5" t="n">
+        <v>465.2</v>
       </c>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
@@ -747,15 +743,23 @@
       <c r="M6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="n"/>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Extra mil: 110 mil: 16.0</t>
+          <t>15.04.2025</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="12" t="n"/>
+      <c r="B7" s="7" t="n">
+        <v>519</v>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Toll: 10.5</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="9" t="n">
+        <v>486.9</v>
+      </c>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
@@ -766,23 +770,15 @@
       <c r="M7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>10.04.2025</t>
+          <t>Charging of rental: 21.7</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>796.5</v>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Toll: 8.8</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="10" t="n">
-        <v>827</v>
-      </c>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="11" t="n"/>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="n"/>
@@ -793,15 +789,27 @@
       <c r="M8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Charging of rental: 21.7</t>
+          <t>14.04.2025</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="12" t="n"/>
+      <c r="B9" s="7" t="n">
+        <v>-256.2</v>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Toll: 3.1</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>toll: 65</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>519</v>
+      </c>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="n"/>
@@ -812,23 +820,19 @@
       <c r="M9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>13.04.2025</t>
+          <t>Charging of rental: 21.7</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>827</v>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Toll: 2.1</t>
+          <t>extra amount : 2.2</t>
         </is>
       </c>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="10" t="n">
-        <v>850.8</v>
-      </c>
+      <c r="E10" s="14" t="n"/>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
@@ -839,15 +843,15 @@
       <c r="M10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Charging of rental: 21.7</t>
+          <t>Rent payment: 650</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="12" t="n"/>
+      <c r="E11" s="14" t="n"/>
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="n"/>
@@ -858,27 +862,15 @@
       <c r="M11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>09.01.2025</t>
+          <t>extra miles: 82.8</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>850.8</v>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Charging of rental: 650</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Rent payment: 650</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>850.8</v>
-      </c>
+      <c r="E12" s="11" t="n"/>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="n"/>
@@ -889,22 +881,22 @@
       <c r="M12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>15.04.2025</t>
+          <t>13.04.2025</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
-        <v>850.8</v>
+      <c r="B13" s="7" t="n">
+        <v>-232.4</v>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Toll: 10.4</t>
+          <t>Toll: 2.1</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="10" t="n">
-        <v>882.9</v>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="16" t="n">
+        <v>-256.2</v>
       </c>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
@@ -916,15 +908,15 @@
       <c r="M13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="11" t="n"/>
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="n"/>
       <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Charging of rental: 21.7</t>
         </is>
       </c>
       <c r="D14" s="3" t="n"/>
-      <c r="E14" s="12" t="n"/>
+      <c r="E14" s="11" t="n"/>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
       <c r="H14" s="2" t="n"/>
@@ -935,22 +927,22 @@
       <c r="M14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>10.02.2025</t>
+          <t>12.04.2025</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
-        <v>882.9</v>
+      <c r="B15" s="7" t="n">
+        <v>-206.6</v>
       </c>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Rent payment: 650</t>
+          <t>Toll: 4.2</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n">
-        <v>232.9</v>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="16" t="n">
+        <v>-232.4</v>
       </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
@@ -962,23 +954,15 @@
       <c r="M15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>12.04.2025</t>
+          <t>Charging of rental: 21.7</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
-        <v>232.9</v>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Toll: 4.2</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="10" t="n">
-        <v>258.8</v>
-      </c>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="11" t="n"/>
       <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="n"/>
@@ -989,15 +973,23 @@
       <c r="M16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="11" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>11.04.2025</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-184.9</v>
+      </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Charging of rental: 21.7</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
-      <c r="E17" s="12" t="n"/>
+      <c r="E17" s="17" t="n">
+        <v>-206.6</v>
+      </c>
       <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
@@ -1008,22 +1000,22 @@
       <c r="M17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>18.04.2025</t>
+          <t>10.04.2025</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
-        <v>258.8</v>
+      <c r="B18" s="7" t="n">
+        <v>-154.4</v>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Charging of rental: 21.7</t>
+          <t>Toll: 8.8</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="5" t="n">
-        <v>280.4999999999999</v>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="16" t="n">
+        <v>-184.9</v>
       </c>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="n"/>
@@ -1035,23 +1027,15 @@
       <c r="M18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>02.04.2025</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>280.4999999999999</v>
-      </c>
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Toll: 8.8</t>
+          <t>Charging of rental: 21.7</t>
         </is>
       </c>
       <c r="D19" s="3" t="n"/>
-      <c r="E19" s="5" t="n">
-        <v>289.3</v>
-      </c>
+      <c r="E19" s="11" t="n"/>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="n"/>
@@ -1062,22 +1046,22 @@
       <c r="M19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>01.04.2025</t>
+          <t>09.04.2025</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>289.3</v>
+      <c r="B20" s="7" t="n">
+        <v>-42.3</v>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Toll: 8.8</t>
+          <t>Toll: 7.6</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="5" t="n">
-        <v>298.1</v>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="16" t="n">
+        <v>-154.4</v>
       </c>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
@@ -1089,23 +1073,15 @@
       <c r="M20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>03.04.2025</t>
+          <t>Extra mil: 552 mil: 82.8</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
-        <v>298.1</v>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Toll: 4.6</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="5" t="n">
-        <v>302.7</v>
-      </c>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="14" t="n"/>
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="n"/>
@@ -1116,23 +1092,15 @@
       <c r="M21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>12.03.2025</t>
+          <t>Charging of rental: 21.7</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>302.7</v>
-      </c>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Rent payment: 650</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="n">
-        <v>-347.3</v>
-      </c>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="11" t="n"/>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
       <c r="H22" s="2" t="n"/>
@@ -1145,20 +1113,20 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>17.04.2025</t>
+          <t>08.04.2025</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-347.3</v>
+        <v>-33.5</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Charging of rental: 21.7</t>
+          <t>Toll: 8.8</t>
         </is>
       </c>
       <c r="D23" s="3" t="n"/>
-      <c r="E23" s="13" t="n">
-        <v>-325.6</v>
+      <c r="E23" s="17" t="n">
+        <v>-42.3</v>
       </c>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
@@ -1170,26 +1138,22 @@
       <c r="M23" s="2" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>14.04.2025</t>
+          <t>07.04.2025</t>
         </is>
       </c>
-      <c r="B24" s="8" t="n">
-        <v>-325.6</v>
+      <c r="B24" s="3" t="n">
+        <v>-24.7</v>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Toll: 3.1</t>
+          <t>Toll: 8.8</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>toll: 65</t>
-        </is>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>-1100.8</v>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="17" t="n">
+        <v>-33.5</v>
       </c>
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="n"/>
@@ -1201,19 +1165,23 @@
       <c r="M24" s="2" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="n"/>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Charging of rental: 21.7</t>
+          <t>05.04.2025</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="B25" s="3" t="n">
+        <v>-22.2</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>extra amount : 2.2</t>
+          <t>Toll: 2.5</t>
         </is>
       </c>
-      <c r="E25" s="17" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="17" t="n">
+        <v>-24.7</v>
+      </c>
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
       <c r="H25" s="2" t="n"/>
@@ -1224,15 +1192,23 @@
       <c r="M25" s="2" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="n"/>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Rent payment: 650</t>
+          <t>03.04.2025</t>
         </is>
       </c>
-      <c r="E26" s="17" t="n"/>
+      <c r="B26" s="3" t="n">
+        <v>-17.6</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Toll: 4.6</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="17" t="n">
+        <v>-22.2</v>
+      </c>
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="n"/>
       <c r="H26" s="2" t="n"/>
@@ -1243,15 +1219,23 @@
       <c r="M26" s="2" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n"/>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>extra miles: 82.8</t>
+          <t>02.04.2025</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n"/>
+      <c r="B27" s="3" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Toll: 8.8</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="17" t="n">
+        <v>-17.6</v>
+      </c>
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
       <c r="H27" s="2" t="n"/>
@@ -1262,22 +1246,22 @@
       <c r="M27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>09.04.2025</t>
+          <t>01.04.2025</t>
         </is>
       </c>
-      <c r="B28" s="8" t="n">
-        <v>-1100.8</v>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Toll: 7.7</t>
+          <t xml:space="preserve"> Toll: 8.8</t>
         </is>
       </c>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="15" t="n">
-        <v>-988.5999999999999</v>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="17" t="n">
+        <v>-8.800000000000001</v>
       </c>
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>
@@ -1289,15 +1273,23 @@
       <c r="M28" s="2" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="n"/>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Extra mil: 552 mil: 82.8</t>
+          <t>29.03.2025</t>
         </is>
       </c>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="17" t="n"/>
+      <c r="B29" s="7" t="n">
+        <v>-116</v>
+      </c>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>за выезд: 100</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
       <c r="H29" s="2" t="n"/>
@@ -1308,15 +1300,15 @@
       <c r="M29" s="2" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n"/>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>Charging of rental: 21.7</t>
+          <t>экстра мили: 16</t>
         </is>
       </c>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="12" t="n"/>
+      <c r="E30" s="11" t="n"/>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
       <c r="H30" s="2" t="n"/>
@@ -1329,20 +1321,20 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>16.04.2025</t>
+          <t>12.03.2025</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-988.5999999999999</v>
+        <v>-766</v>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>Charging of rental: 21.7</t>
+          <t>Rent payment: 650</t>
         </is>
       </c>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="13" t="n">
-        <v>-966.8999999999999</v>
+      <c r="E31" s="17" t="n">
+        <v>-116</v>
       </c>
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
@@ -1354,22 +1346,22 @@
       <c r="M31" s="2" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>29.03.2025</t>
+          <t>09.03.2025</t>
         </is>
       </c>
-      <c r="B32" s="8" t="n">
-        <v>-966.8999999999999</v>
+      <c r="B32" s="3" t="n">
+        <v>-116</v>
       </c>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="14" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>за выезд: 100</t>
+          <t>Charging of rental: 650</t>
         </is>
       </c>
-      <c r="E32" s="15" t="n">
-        <v>-1082.9</v>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="17" t="n">
+        <v>-766</v>
       </c>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
@@ -1381,15 +1373,23 @@
       <c r="M32" s="2" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>экстра мили: 16</t>
+          <t>10.02.2025</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n"/>
+      <c r="B33" s="3" t="n">
+        <v>-766</v>
+      </c>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>Rent payment: 650</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>-116</v>
+      </c>
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
       <c r="H33" s="2" t="n"/>
@@ -1400,22 +1400,22 @@
       <c r="M33" s="2" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>05.04.2025</t>
+          <t>09.02.2025</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
-        <v>-1082.9</v>
+      <c r="B34" s="7" t="n">
+        <v>-100</v>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Toll: 2.4</t>
+          <t>Charging of rental: 650</t>
         </is>
       </c>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="13" t="n">
-        <v>-1080.5</v>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="16" t="n">
+        <v>-766</v>
       </c>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
@@ -1427,23 +1427,15 @@
       <c r="M34" s="2" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>19.04.2025</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>-1080.5</v>
-      </c>
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Charging of rental: 21.7</t>
+          <t>Extra mil: 110 mil: 16.0</t>
         </is>
       </c>
       <c r="D35" s="3" t="n"/>
-      <c r="E35" s="13" t="n">
-        <v>-1058.8</v>
-      </c>
+      <c r="E35" s="11" t="n"/>
       <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="n"/>
       <c r="H35" s="2" t="n"/>
@@ -1456,20 +1448,24 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>09.03.2025</t>
+          <t>09.01.2025</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-1058.8</v>
+        <v>-100</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Charging of rental: 650</t>
         </is>
       </c>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="13" t="n">
-        <v>-408.7999999999997</v>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>Rent payment: 650</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>-100</v>
       </c>
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
@@ -1483,20 +1479,20 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>08.04.2025</t>
+          <t>18.12.2024</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>-408.7999999999997</v>
+        <v>0</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Toll: 8.8</t>
+          <t>100$ Денису должен за выезд : 100</t>
         </is>
       </c>
       <c r="D37" s="3" t="n"/>
-      <c r="E37" s="13" t="n">
-        <v>-399.9999999999997</v>
+      <c r="E37" s="17" t="n">
+        <v>-100</v>
       </c>
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
@@ -1508,11 +1504,27 @@
       <c r="M37" s="2" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n"/>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>09.12.2024</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Charging of rental: 650</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>Rent payment: 650</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="F38" s="2" t="n"/>
       <c r="G38" s="2" t="n"/>
       <c r="H38" s="2" t="n"/>
@@ -15954,30 +15966,30 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="B18:B19"/>
     <mergeCell ref="E13:E14"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="E9:E12"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="B9:B12"/>
     <mergeCell ref="A13:A14"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="E24:E27"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B7:B8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
